--- a/Competitor360_Master.xlsx
+++ b/Competitor360_Master.xlsx
@@ -440,6 +440,11 @@
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
         <t>Contact says 11,900 — confirm IFZA 11,900 vs 12,900</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Official RAKEZ package list, 23 Feb 2026 (via SPC)</t>
       </text>
     </comment>
     <comment ref="E7" authorId="0" shapeId="0">
@@ -1091,7 +1096,7 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Key insight: take-home = rate × base. A lower rate on a bigger base can beat a higher rate on a small one — Meydan 30%×12,500 = 3,750 beats RAKEZ 50%×6,010 = 3,005.</t>
+          <t>Key insight: take-home = rate × base. A lower rate on a bigger base can beat a higher rate on a small one — Meydan 30%×12,500 = 3,750 beats RAKEZ 50%×6,000 = 3,000.</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1181,7 @@
         <v>12900</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>6010</v>
+        <v>6000</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>4888</v>
@@ -1644,7 +1649,7 @@
         <v>14900</v>
       </c>
       <c r="D7" s="22" t="n">
-        <v>6010</v>
+        <v>6000</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>10800</v>
@@ -2088,7 +2093,7 @@
     <row r="29">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>Key: take-home = rate × base. A lower rate on a bigger base can beat a higher rate on a small one — Meydan 30%×12,500 = 3,750 beats RAKEZ 50%×6,010 = 3,005.</t>
+          <t>Key: take-home = rate × base. A lower rate on a bigger base can beat a higher rate on a small one — Meydan 30%×12,500 = 3,750 beats RAKEZ 50%×6,000 = 3,000.</t>
         </is>
       </c>
     </row>
@@ -2243,25 +2248,25 @@
     </row>
     <row r="10">
       <c r="A10" s="21" t="n">
-        <v>14010</v>
+        <v>14000</v>
       </c>
       <c r="B10" s="21" t="n">
-        <v>26620</v>
+        <v>26600</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>37830</v>
+        <v>37800</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>50440</v>
+        <v>50400</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>59560</v>
+        <v>59500</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>67260</v>
+        <v>67200</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>105100</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="12">
@@ -2316,7 +2321,7 @@
         <v>17100</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>14010</v>
+        <v>14000</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>9900</v>
